--- a/data/nzd0063/nzd0063.xlsx
+++ b/data/nzd0063/nzd0063.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q350"/>
+  <dimension ref="A1:Q352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20402,6 +20402,120 @@
       <c r="Q350" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>356.27</v>
+      </c>
+      <c r="C351" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="D351" t="n">
+        <v>352.34</v>
+      </c>
+      <c r="E351" t="n">
+        <v>355.65</v>
+      </c>
+      <c r="F351" t="n">
+        <v>362.31</v>
+      </c>
+      <c r="G351" t="n">
+        <v>359.03</v>
+      </c>
+      <c r="H351" t="n">
+        <v>362.12</v>
+      </c>
+      <c r="I351" t="n">
+        <v>356.71</v>
+      </c>
+      <c r="J351" t="n">
+        <v>356.52</v>
+      </c>
+      <c r="K351" t="n">
+        <v>354.42</v>
+      </c>
+      <c r="L351" t="n">
+        <v>358.67</v>
+      </c>
+      <c r="M351" t="n">
+        <v>359.44</v>
+      </c>
+      <c r="N351" t="n">
+        <v>358.96</v>
+      </c>
+      <c r="O351" t="n">
+        <v>362.71</v>
+      </c>
+      <c r="P351" t="n">
+        <v>361.86</v>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>354.37</v>
+      </c>
+      <c r="C352" t="n">
+        <v>342.79</v>
+      </c>
+      <c r="D352" t="n">
+        <v>352.18</v>
+      </c>
+      <c r="E352" t="n">
+        <v>353.13</v>
+      </c>
+      <c r="F352" t="n">
+        <v>364.72</v>
+      </c>
+      <c r="G352" t="n">
+        <v>358.37</v>
+      </c>
+      <c r="H352" t="n">
+        <v>362.22</v>
+      </c>
+      <c r="I352" t="n">
+        <v>355.77</v>
+      </c>
+      <c r="J352" t="n">
+        <v>355.62</v>
+      </c>
+      <c r="K352" t="n">
+        <v>354.99</v>
+      </c>
+      <c r="L352" t="n">
+        <v>358.06</v>
+      </c>
+      <c r="M352" t="n">
+        <v>358.42</v>
+      </c>
+      <c r="N352" t="n">
+        <v>357.97</v>
+      </c>
+      <c r="O352" t="n">
+        <v>361.97</v>
+      </c>
+      <c r="P352" t="n">
+        <v>361.57</v>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20416,7 +20530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B357"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23989,6 +24103,26 @@
       </c>
       <c r="B357" t="n">
         <v>0.86</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -24157,28 +24291,28 @@
         <v>0.0544</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07420678998281945</v>
+        <v>0.0728376743940909</v>
       </c>
       <c r="J2" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K2" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02083180662774897</v>
+        <v>0.02033411257850104</v>
       </c>
       <c r="M2" t="n">
-        <v>2.96593103359104</v>
+        <v>2.955153088244679</v>
       </c>
       <c r="N2" t="n">
-        <v>14.45108447956122</v>
+        <v>14.381672153598</v>
       </c>
       <c r="O2" t="n">
-        <v>3.801458204368584</v>
+        <v>3.792317517507995</v>
       </c>
       <c r="P2" t="n">
-        <v>354.5091334391608</v>
+        <v>354.5235099686156</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24239,28 +24373,28 @@
         <v>0.06</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02606820736994616</v>
+        <v>-0.02650081597954628</v>
       </c>
       <c r="J3" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K3" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003971906210023968</v>
+        <v>0.004158868772608848</v>
       </c>
       <c r="M3" t="n">
-        <v>2.227506085318431</v>
+        <v>2.217268908533923</v>
       </c>
       <c r="N3" t="n">
-        <v>9.514319351097919</v>
+        <v>9.461888281814876</v>
       </c>
       <c r="O3" t="n">
-        <v>3.084529032299407</v>
+        <v>3.076018251216152</v>
       </c>
       <c r="P3" t="n">
-        <v>344.2861132319841</v>
+        <v>344.290656531583</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -24321,28 +24455,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01047824908299044</v>
+        <v>0.01078714564542035</v>
       </c>
       <c r="J4" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K4" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004618126700624003</v>
+        <v>0.000496032308632266</v>
       </c>
       <c r="M4" t="n">
-        <v>2.693400313896018</v>
+        <v>2.679391477139593</v>
       </c>
       <c r="N4" t="n">
-        <v>13.3008378468738</v>
+        <v>13.22526941949374</v>
       </c>
       <c r="O4" t="n">
-        <v>3.64703137453927</v>
+        <v>3.636656351580905</v>
       </c>
       <c r="P4" t="n">
-        <v>351.7139533289089</v>
+        <v>351.7107137170048</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24403,28 +24537,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02269514145472795</v>
+        <v>-0.02665198145711369</v>
       </c>
       <c r="J5" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K5" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003162089974751203</v>
+        <v>0.004378547387650644</v>
       </c>
       <c r="M5" t="n">
-        <v>2.311511631975544</v>
+        <v>2.318888684267985</v>
       </c>
       <c r="N5" t="n">
-        <v>9.065648944259847</v>
+        <v>9.087986569487493</v>
       </c>
       <c r="O5" t="n">
-        <v>3.010921610447513</v>
+        <v>3.014628761470887</v>
       </c>
       <c r="P5" t="n">
-        <v>358.4106298312415</v>
+        <v>358.4521708815851</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -24485,28 +24619,28 @@
         <v>0.0949</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0643985588836265</v>
+        <v>-0.0637615063205237</v>
       </c>
       <c r="J6" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K6" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02781394123496805</v>
+        <v>0.02760741248057819</v>
       </c>
       <c r="M6" t="n">
-        <v>2.182621267486001</v>
+        <v>2.177112479487316</v>
       </c>
       <c r="N6" t="n">
-        <v>8.093231081094242</v>
+        <v>8.057077712771918</v>
       </c>
       <c r="O6" t="n">
-        <v>2.844860467772408</v>
+        <v>2.838499200769998</v>
       </c>
       <c r="P6" t="n">
-        <v>364.7003187811756</v>
+        <v>364.6936251928406</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -24567,28 +24701,28 @@
         <v>0.1142</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01717883108653936</v>
+        <v>-0.02161910268240036</v>
       </c>
       <c r="J7" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K7" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001718649117754989</v>
+        <v>0.002732300980226476</v>
       </c>
       <c r="M7" t="n">
-        <v>2.472747509346977</v>
+        <v>2.478813232644561</v>
       </c>
       <c r="N7" t="n">
-        <v>9.570524610443483</v>
+        <v>9.59849235921909</v>
       </c>
       <c r="O7" t="n">
-        <v>3.093626449725869</v>
+        <v>3.098143372928227</v>
       </c>
       <c r="P7" t="n">
-        <v>362.9923505860631</v>
+        <v>363.0389610731588</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -24649,28 +24783,28 @@
         <v>0.1166</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02772544807006677</v>
+        <v>0.02699781917039503</v>
       </c>
       <c r="J8" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K8" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004101698083788019</v>
+        <v>0.003941706139237611</v>
       </c>
       <c r="M8" t="n">
-        <v>2.532528213340065</v>
+        <v>2.521660573192678</v>
       </c>
       <c r="N8" t="n">
-        <v>10.42056425685038</v>
+        <v>10.36340237848574</v>
       </c>
       <c r="O8" t="n">
-        <v>3.228089877443065</v>
+        <v>3.219223878279629</v>
       </c>
       <c r="P8" t="n">
-        <v>362.0508077700611</v>
+        <v>362.0584452732812</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -24731,28 +24865,28 @@
         <v>0.1574</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07403666400957831</v>
+        <v>0.06771139313391109</v>
       </c>
       <c r="J9" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K9" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03618791894982842</v>
+        <v>0.03024312910708871</v>
       </c>
       <c r="M9" t="n">
-        <v>2.35019938965372</v>
+        <v>2.366308789182498</v>
       </c>
       <c r="N9" t="n">
-        <v>8.150893662349686</v>
+        <v>8.271878004563494</v>
       </c>
       <c r="O9" t="n">
-        <v>2.854976998567534</v>
+        <v>2.876087273460855</v>
       </c>
       <c r="P9" t="n">
-        <v>359.7054914153319</v>
+        <v>359.77188915844</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -24813,28 +24947,28 @@
         <v>0.1396</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06896546192133987</v>
+        <v>0.06463014476357887</v>
       </c>
       <c r="J10" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K10" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02520552480353921</v>
+        <v>0.02232904414325199</v>
       </c>
       <c r="M10" t="n">
-        <v>2.225891668574036</v>
+        <v>2.235622571459928</v>
       </c>
       <c r="N10" t="n">
-        <v>10.26983344941572</v>
+        <v>10.29051994847675</v>
       </c>
       <c r="O10" t="n">
-        <v>3.204658086195112</v>
+        <v>3.207884029773637</v>
       </c>
       <c r="P10" t="n">
-        <v>357.9505858453839</v>
+        <v>357.9960953002524</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -24895,28 +25029,28 @@
         <v>0.1321</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02561127685134056</v>
+        <v>-0.02929287653792706</v>
       </c>
       <c r="J11" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K11" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002597702952423342</v>
+        <v>0.0034274617375879</v>
       </c>
       <c r="M11" t="n">
-        <v>2.885484146505354</v>
+        <v>2.891825329824871</v>
       </c>
       <c r="N11" t="n">
-        <v>14.06132106189692</v>
+        <v>14.0379865762772</v>
       </c>
       <c r="O11" t="n">
-        <v>3.749842804958218</v>
+        <v>3.746730117886421</v>
       </c>
       <c r="P11" t="n">
-        <v>358.5674875825608</v>
+        <v>358.6061310633104</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -24977,28 +25111,28 @@
         <v>0.08840000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01450274736794519</v>
+        <v>0.009628176012844056</v>
       </c>
       <c r="J12" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K12" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0007995027503772123</v>
+        <v>0.0003548961757112723</v>
       </c>
       <c r="M12" t="n">
-        <v>2.964223773557962</v>
+        <v>2.968722706573321</v>
       </c>
       <c r="N12" t="n">
-        <v>14.6762813888899</v>
+        <v>14.69186895395938</v>
       </c>
       <c r="O12" t="n">
-        <v>3.830963506598556</v>
+        <v>3.832997385070772</v>
       </c>
       <c r="P12" t="n">
-        <v>362.1801100626448</v>
+        <v>362.2312791748959</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -25059,28 +25193,28 @@
         <v>0.09229999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0374056135343164</v>
+        <v>-0.03997935339730575</v>
       </c>
       <c r="J13" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K13" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01137219946975387</v>
+        <v>0.01308791710790991</v>
       </c>
       <c r="M13" t="n">
-        <v>2.030953320556862</v>
+        <v>2.031179350458746</v>
       </c>
       <c r="N13" t="n">
-        <v>6.79117156395412</v>
+        <v>6.781471520556463</v>
       </c>
       <c r="O13" t="n">
-        <v>2.60598763695343</v>
+        <v>2.604125864960536</v>
       </c>
       <c r="P13" t="n">
-        <v>362.1528624033026</v>
+        <v>362.1798812529555</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -25141,28 +25275,28 @@
         <v>0.1044</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.008790979959426525</v>
+        <v>-0.01341514160424398</v>
       </c>
       <c r="J14" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K14" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0003839919803195757</v>
+        <v>0.0008985965523742312</v>
       </c>
       <c r="M14" t="n">
-        <v>2.409764211465938</v>
+        <v>2.422858498042128</v>
       </c>
       <c r="N14" t="n">
-        <v>11.23229277676428</v>
+        <v>11.25848163510938</v>
       </c>
       <c r="O14" t="n">
-        <v>3.351461289760673</v>
+        <v>3.355366095541495</v>
       </c>
       <c r="P14" t="n">
-        <v>362.685104003158</v>
+        <v>362.733645647151</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -25223,28 +25357,28 @@
         <v>0.1029</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.03025889476713659</v>
+        <v>-0.03320338976718543</v>
       </c>
       <c r="J15" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K15" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L15" t="n">
-        <v>0.004904322211802925</v>
+        <v>0.005957551888375878</v>
       </c>
       <c r="M15" t="n">
-        <v>2.379184313432011</v>
+        <v>2.3806026014507</v>
       </c>
       <c r="N15" t="n">
-        <v>10.39824347320615</v>
+        <v>10.37573399435277</v>
       </c>
       <c r="O15" t="n">
-        <v>3.224630749900856</v>
+        <v>3.221138617686729</v>
       </c>
       <c r="P15" t="n">
-        <v>365.6891558004698</v>
+        <v>365.7200430503344</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -25305,28 +25439,28 @@
         <v>0.1246</v>
       </c>
       <c r="I16" t="n">
-        <v>0.003722648846086701</v>
+        <v>0.003241164143706122</v>
       </c>
       <c r="J16" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K16" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0001020956642765469</v>
+        <v>7.843153476005948e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>2.19346247611366</v>
+        <v>2.183393488786578</v>
       </c>
       <c r="N16" t="n">
-        <v>7.596622015891981</v>
+        <v>7.554298817163188</v>
       </c>
       <c r="O16" t="n">
-        <v>2.756197020514314</v>
+        <v>2.748508471364639</v>
       </c>
       <c r="P16" t="n">
-        <v>362.0276739077214</v>
+        <v>362.0327250631306</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -25368,7 +25502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q350"/>
+  <dimension ref="A1:Q352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55809,6 +55943,180 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-35.221196231026305,174.05921462906713</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-35.22180160002356,174.05868506652902</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-35.22250736758016,174.05836629976767</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-35.22325487268038,174.05825826692643</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-35.223991495158835,174.05828656533663</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-35.224726380193324,174.0582723233428</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-35.22545913500924,174.0583281730987</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-35.226194537089704,174.05829339622076</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>-35.226928188155355,174.0583212506358</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>-35.2276624118927,174.05832813750803</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>-35.2283973531038,174.05840625897923</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>-35.22912205024416,174.05858308383787</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>-35.22982619858072,174.05884528743266</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>-35.23048787307922,174.05923035896112</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>-35.23110090599301,174.05972528483883</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-35.221188630460475,174.0591959208131</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>-35.22179827159952,174.0586767763605</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>-35.22250694316423,174.05836461960808</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-35.22325272096272,174.05823070317675</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-35.22399161379968,174.05831304476388</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-35.22472656607467,174.0582650750808</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-35.22545910548193,174.05832927127685</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-35.22619485242579,174.058283074864</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-35.22692851398195,174.0583113695247</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-35.22766220142344,174.05833439539796</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-35.22839800063027,174.05839960287355</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-35.22912433293752,174.05857222666137</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>-35.22982930657037,174.05883508981282</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>-35.23049108273135,174.05922323032922</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>-35.231102380933045,174.0597226536142</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0063/nzd0063.xlsx
+++ b/data/nzd0063/nzd0063.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q352"/>
+  <dimension ref="A1:Q354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20516,6 +20516,120 @@
       <c r="Q352" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>353.2</v>
+      </c>
+      <c r="C353" t="n">
+        <v>344.1</v>
+      </c>
+      <c r="D353" t="n">
+        <v>353.54</v>
+      </c>
+      <c r="E353" t="n">
+        <v>354.55</v>
+      </c>
+      <c r="F353" t="n">
+        <v>365.67</v>
+      </c>
+      <c r="G353" t="n">
+        <v>360.24</v>
+      </c>
+      <c r="H353" t="n">
+        <v>362.2</v>
+      </c>
+      <c r="I353" t="n">
+        <v>356.06</v>
+      </c>
+      <c r="J353" t="n">
+        <v>355.86</v>
+      </c>
+      <c r="K353" t="n">
+        <v>355.41</v>
+      </c>
+      <c r="L353" t="n">
+        <v>360.4</v>
+      </c>
+      <c r="M353" t="n">
+        <v>358.62</v>
+      </c>
+      <c r="N353" t="n">
+        <v>358.55</v>
+      </c>
+      <c r="O353" t="n">
+        <v>363.24</v>
+      </c>
+      <c r="P353" t="n">
+        <v>363.13</v>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>353.96</v>
+      </c>
+      <c r="C354" t="n">
+        <v>344.16</v>
+      </c>
+      <c r="D354" t="n">
+        <v>353.66</v>
+      </c>
+      <c r="E354" t="n">
+        <v>355.14</v>
+      </c>
+      <c r="F354" t="n">
+        <v>365.88</v>
+      </c>
+      <c r="G354" t="n">
+        <v>361.47</v>
+      </c>
+      <c r="H354" t="n">
+        <v>362.57</v>
+      </c>
+      <c r="I354" t="n">
+        <v>357.36</v>
+      </c>
+      <c r="J354" t="n">
+        <v>356.59</v>
+      </c>
+      <c r="K354" t="n">
+        <v>356.08</v>
+      </c>
+      <c r="L354" t="n">
+        <v>360.71</v>
+      </c>
+      <c r="M354" t="n">
+        <v>359.21</v>
+      </c>
+      <c r="N354" t="n">
+        <v>359.19</v>
+      </c>
+      <c r="O354" t="n">
+        <v>363.83</v>
+      </c>
+      <c r="P354" t="n">
+        <v>363.63</v>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20530,7 +20644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B359"/>
+  <dimension ref="A1:B361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24123,6 +24237,26 @@
       </c>
       <c r="B359" t="n">
         <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -24291,28 +24425,28 @@
         <v>0.0544</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0728376743940909</v>
+        <v>0.06951265771091082</v>
       </c>
       <c r="J2" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K2" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02033411257850104</v>
+        <v>0.0187356321633253</v>
       </c>
       <c r="M2" t="n">
-        <v>2.955153088244679</v>
+        <v>2.953242502738564</v>
       </c>
       <c r="N2" t="n">
-        <v>14.381672153598</v>
+        <v>14.34790219461951</v>
       </c>
       <c r="O2" t="n">
-        <v>3.792317517507995</v>
+        <v>3.787862483594079</v>
       </c>
       <c r="P2" t="n">
-        <v>354.5235099686156</v>
+        <v>354.558503148756</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24373,28 +24507,28 @@
         <v>0.06</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02650081597954628</v>
+        <v>-0.02586239644969964</v>
       </c>
       <c r="J3" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K3" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004158868772608848</v>
+        <v>0.004013687699644941</v>
       </c>
       <c r="M3" t="n">
-        <v>2.217268908533923</v>
+        <v>2.207718393802073</v>
       </c>
       <c r="N3" t="n">
-        <v>9.461888281814876</v>
+        <v>9.410013908396953</v>
       </c>
       <c r="O3" t="n">
-        <v>3.076018251216152</v>
+        <v>3.067574597038669</v>
       </c>
       <c r="P3" t="n">
-        <v>344.290656531583</v>
+        <v>344.2839371116003</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -24455,28 +24589,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01078714564542035</v>
+        <v>0.0126194082027734</v>
       </c>
       <c r="J4" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K4" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000496032308632266</v>
+        <v>0.0006870366898882319</v>
       </c>
       <c r="M4" t="n">
-        <v>2.679391477139593</v>
+        <v>2.672268265659703</v>
       </c>
       <c r="N4" t="n">
-        <v>13.22526941949374</v>
+        <v>13.16443373438018</v>
       </c>
       <c r="O4" t="n">
-        <v>3.636656351580905</v>
+        <v>3.628282477203253</v>
       </c>
       <c r="P4" t="n">
-        <v>351.7107137170048</v>
+        <v>351.6914430129014</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24537,28 +24671,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02665198145711369</v>
+        <v>-0.02996036587002025</v>
       </c>
       <c r="J5" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K5" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004378547387650644</v>
+        <v>0.005571350327541635</v>
       </c>
       <c r="M5" t="n">
-        <v>2.318888684267985</v>
+        <v>2.323374188891584</v>
       </c>
       <c r="N5" t="n">
-        <v>9.087986569487493</v>
+        <v>9.083439511038412</v>
       </c>
       <c r="O5" t="n">
-        <v>3.014628761470887</v>
+        <v>3.013874501540901</v>
       </c>
       <c r="P5" t="n">
-        <v>358.4521708815851</v>
+        <v>358.4869894337951</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -24619,28 +24753,28 @@
         <v>0.0949</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0637615063205237</v>
+        <v>-0.06055710253729725</v>
       </c>
       <c r="J6" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K6" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02760741248057819</v>
+        <v>0.02516157310792577</v>
       </c>
       <c r="M6" t="n">
-        <v>2.177112479487316</v>
+        <v>2.18085837957749</v>
       </c>
       <c r="N6" t="n">
-        <v>8.057077712771918</v>
+        <v>8.055044951719999</v>
       </c>
       <c r="O6" t="n">
-        <v>2.838499200769998</v>
+        <v>2.838141108493374</v>
       </c>
       <c r="P6" t="n">
-        <v>364.6936251928406</v>
+        <v>364.6598988335126</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -24701,28 +24835,28 @@
         <v>0.1142</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02161910268240036</v>
+        <v>-0.02345253599108926</v>
       </c>
       <c r="J7" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K7" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002732300980226476</v>
+        <v>0.003251082017318385</v>
       </c>
       <c r="M7" t="n">
-        <v>2.478813232644561</v>
+        <v>2.473301366909071</v>
       </c>
       <c r="N7" t="n">
-        <v>9.59849235921909</v>
+        <v>9.560495743213766</v>
       </c>
       <c r="O7" t="n">
-        <v>3.098143372928227</v>
+        <v>3.092005133115688</v>
       </c>
       <c r="P7" t="n">
-        <v>363.0389610731588</v>
+        <v>363.0582543281777</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -24783,28 +24917,28 @@
         <v>0.1166</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02699781917039503</v>
+        <v>0.02654240782739824</v>
       </c>
       <c r="J8" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K8" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003941706139237611</v>
+        <v>0.003860680427535734</v>
       </c>
       <c r="M8" t="n">
-        <v>2.521660573192678</v>
+        <v>2.509578645024778</v>
       </c>
       <c r="N8" t="n">
-        <v>10.36340237848574</v>
+        <v>10.3057548645311</v>
       </c>
       <c r="O8" t="n">
-        <v>3.219223878279629</v>
+        <v>3.210257756712239</v>
       </c>
       <c r="P8" t="n">
-        <v>362.0584452732812</v>
+        <v>362.0632374111959</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -24865,28 +24999,28 @@
         <v>0.1574</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06771139313391109</v>
+        <v>0.06211923240956585</v>
       </c>
       <c r="J9" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K9" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03024312910708871</v>
+        <v>0.02550142837645086</v>
       </c>
       <c r="M9" t="n">
-        <v>2.366308789182498</v>
+        <v>2.378763664823552</v>
       </c>
       <c r="N9" t="n">
-        <v>8.271878004563494</v>
+        <v>8.360106398522143</v>
       </c>
       <c r="O9" t="n">
-        <v>2.876087273460855</v>
+        <v>2.891384858250825</v>
       </c>
       <c r="P9" t="n">
-        <v>359.77188915844</v>
+        <v>359.8307421434018</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -24947,28 +25081,28 @@
         <v>0.1396</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06463014476357887</v>
+        <v>0.06061385945740513</v>
       </c>
       <c r="J10" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K10" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02232904414325199</v>
+        <v>0.01981965951977271</v>
       </c>
       <c r="M10" t="n">
-        <v>2.235622571459928</v>
+        <v>2.244009538932414</v>
       </c>
       <c r="N10" t="n">
-        <v>10.29051994847675</v>
+        <v>10.30140867249356</v>
       </c>
       <c r="O10" t="n">
-        <v>3.207884029773637</v>
+        <v>3.209580762731102</v>
       </c>
       <c r="P10" t="n">
-        <v>357.9960953002524</v>
+        <v>358.0383640258416</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -25029,28 +25163,28 @@
         <v>0.1321</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02929287653792706</v>
+        <v>-0.03166422877935191</v>
       </c>
       <c r="J11" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K11" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0034274617375879</v>
+        <v>0.004048742305712172</v>
       </c>
       <c r="M11" t="n">
-        <v>2.891825329824871</v>
+        <v>2.889960678966538</v>
       </c>
       <c r="N11" t="n">
-        <v>14.0379865762772</v>
+        <v>13.98294731642031</v>
       </c>
       <c r="O11" t="n">
-        <v>3.746730117886421</v>
+        <v>3.739377931744839</v>
       </c>
       <c r="P11" t="n">
-        <v>358.6061310633104</v>
+        <v>358.6310873180374</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -25111,28 +25245,28 @@
         <v>0.08840000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.009628176012844056</v>
+        <v>0.007413789564593538</v>
       </c>
       <c r="J12" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K12" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0003548961757112723</v>
+        <v>0.0002129606596887879</v>
       </c>
       <c r="M12" t="n">
-        <v>2.968722706573321</v>
+        <v>2.961503237692677</v>
       </c>
       <c r="N12" t="n">
-        <v>14.69186895395938</v>
+        <v>14.62957035056226</v>
       </c>
       <c r="O12" t="n">
-        <v>3.832997385070772</v>
+        <v>3.82486213484385</v>
       </c>
       <c r="P12" t="n">
-        <v>362.2312791748959</v>
+        <v>362.2545843603071</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -25193,28 +25327,28 @@
         <v>0.09229999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.03997935339730575</v>
+        <v>-0.04248549700557974</v>
       </c>
       <c r="J13" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K13" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01308791710790991</v>
+        <v>0.01489044849136101</v>
       </c>
       <c r="M13" t="n">
-        <v>2.031179350458746</v>
+        <v>2.031050914935188</v>
       </c>
       <c r="N13" t="n">
-        <v>6.781471520556463</v>
+        <v>6.770193799902702</v>
       </c>
       <c r="O13" t="n">
-        <v>2.604125864960536</v>
+        <v>2.601959607661637</v>
       </c>
       <c r="P13" t="n">
-        <v>362.1798812529555</v>
+        <v>362.2062563758986</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -25275,28 +25409,28 @@
         <v>0.1044</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.01341514160424398</v>
+        <v>-0.0174229651936018</v>
       </c>
       <c r="J14" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K14" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0008985965523742312</v>
+        <v>0.001525645355505256</v>
       </c>
       <c r="M14" t="n">
-        <v>2.422858498042128</v>
+        <v>2.432391392683699</v>
       </c>
       <c r="N14" t="n">
-        <v>11.25848163510938</v>
+        <v>11.26342326632885</v>
       </c>
       <c r="O14" t="n">
-        <v>3.355366095541495</v>
+        <v>3.356102392110356</v>
       </c>
       <c r="P14" t="n">
-        <v>362.733645647151</v>
+        <v>362.7758255563896</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -25357,28 +25491,28 @@
         <v>0.1029</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.03320338976718543</v>
+        <v>-0.03467836844413097</v>
       </c>
       <c r="J15" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K15" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L15" t="n">
-        <v>0.005957551888375878</v>
+        <v>0.006575067318400518</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3806026014507</v>
+        <v>2.374515281951684</v>
       </c>
       <c r="N15" t="n">
-        <v>10.37573399435277</v>
+        <v>10.32653875331306</v>
       </c>
       <c r="O15" t="n">
-        <v>3.221138617686729</v>
+        <v>3.213493232187218</v>
       </c>
       <c r="P15" t="n">
-        <v>365.7200430503344</v>
+        <v>365.7355541897739</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -25439,28 +25573,28 @@
         <v>0.1246</v>
       </c>
       <c r="I16" t="n">
-        <v>0.003241164143706122</v>
+        <v>0.00468257047695732</v>
       </c>
       <c r="J16" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K16" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L16" t="n">
-        <v>7.843153476005948e-05</v>
+        <v>0.0001656715547418974</v>
       </c>
       <c r="M16" t="n">
-        <v>2.183393488786578</v>
+        <v>2.177732506067374</v>
       </c>
       <c r="N16" t="n">
-        <v>7.554298817163188</v>
+        <v>7.520580346729909</v>
       </c>
       <c r="O16" t="n">
-        <v>2.748508471364639</v>
+        <v>2.742367653457484</v>
       </c>
       <c r="P16" t="n">
-        <v>362.0327250631306</v>
+        <v>362.0175640363022</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -25502,7 +25636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q352"/>
+  <dimension ref="A1:Q354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56117,6 +56251,180 @@
         </is>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-35.221183950110586,174.05918440046884</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-35.22180346235582,174.05868970507598</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-35.22251055069891,174.05837890096518</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-35.22325393343933,174.0582462351308</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-35.22399166056525,174.05832348271235</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-35.22472603940974,174.05828561182304</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-35.22545911138741,174.05832905164124</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-35.22619475514135,174.05828625911235</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-35.22692842709494,174.05831400448764</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-35.227662046340626,174.05833900647477</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>-35.22839551667431,174.05842513613075</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>-35.22912388535065,174.05857435551957</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>-35.229827485728045,174.05884106417605</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>-35.23048557427407,174.05923546460252</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>-35.23109444677225,174.0597368077871</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>-35.22118699033799,174.05919188376922</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>-35.22180370010036,174.05869029723092</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-35.2225108690107,174.05838016108495</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-35.22325443721422,174.05825268854844</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-35.22399167090276,174.05832579004834</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-35.224725692991896,174.0582991199474</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-35.22545900213627,174.0583331149005</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-35.226194319037646,174.05830053332912</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-35.22692816281325,174.05832201916664</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>-35.227661798946244,174.05834636224006</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>-35.22839518760283,174.05842851874166</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>-35.22912256496921,174.05858063565108</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>-35.229825476522386,174.05884765657657</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>-35.23048301522658,174.05924114824074</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>-35.231091903771656,174.05974134438037</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0063/nzd0063.xlsx
+++ b/data/nzd0063/nzd0063.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q354"/>
+  <dimension ref="A1:Q355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20628,6 +20628,63 @@
         <v>363.63</v>
       </c>
       <c r="Q354" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>354.86</v>
+      </c>
+      <c r="C355" t="n">
+        <v>344.27</v>
+      </c>
+      <c r="D355" t="n">
+        <v>353.71</v>
+      </c>
+      <c r="E355" t="n">
+        <v>355.94</v>
+      </c>
+      <c r="F355" t="n">
+        <v>366.1</v>
+      </c>
+      <c r="G355" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="H355" t="n">
+        <v>362.18</v>
+      </c>
+      <c r="I355" t="n">
+        <v>357.75</v>
+      </c>
+      <c r="J355" t="n">
+        <v>355.87</v>
+      </c>
+      <c r="K355" t="n">
+        <v>354.96</v>
+      </c>
+      <c r="L355" t="n">
+        <v>358.71</v>
+      </c>
+      <c r="M355" t="n">
+        <v>359.04</v>
+      </c>
+      <c r="N355" t="n">
+        <v>359.14</v>
+      </c>
+      <c r="O355" t="n">
+        <v>364.21</v>
+      </c>
+      <c r="P355" t="n">
+        <v>363.94</v>
+      </c>
+      <c r="Q355" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20644,7 +20701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B361"/>
+  <dimension ref="A1:B362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24257,6 +24314,16 @@
       </c>
       <c r="B361" t="n">
         <v>0.43</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -24425,28 +24492,28 @@
         <v>0.0544</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06951265771091082</v>
+        <v>0.06861125403611269</v>
       </c>
       <c r="J2" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K2" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0187356321633253</v>
+        <v>0.01837216562613597</v>
       </c>
       <c r="M2" t="n">
-        <v>2.953242502738564</v>
+        <v>2.94899718066093</v>
       </c>
       <c r="N2" t="n">
-        <v>14.34790219461951</v>
+        <v>14.31432329068504</v>
       </c>
       <c r="O2" t="n">
-        <v>3.787862483594079</v>
+        <v>3.783427452811146</v>
       </c>
       <c r="P2" t="n">
-        <v>354.558503148756</v>
+        <v>354.5680283206196</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24507,28 +24574,28 @@
         <v>0.06</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02586239644969964</v>
+        <v>-0.02547188092211176</v>
       </c>
       <c r="J3" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K3" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004013687699644941</v>
+        <v>0.003919116174376014</v>
       </c>
       <c r="M3" t="n">
-        <v>2.207718393802073</v>
+        <v>2.203304432009371</v>
       </c>
       <c r="N3" t="n">
-        <v>9.410013908396953</v>
+        <v>9.384736739522079</v>
       </c>
       <c r="O3" t="n">
-        <v>3.067574597038669</v>
+        <v>3.06345176876054</v>
       </c>
       <c r="P3" t="n">
-        <v>344.2839371116003</v>
+        <v>344.2798105170237</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -24589,28 +24656,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0126194082027734</v>
+        <v>0.01358036216846624</v>
       </c>
       <c r="J4" t="n">
+        <v>354</v>
+      </c>
+      <c r="K4" t="n">
         <v>353</v>
       </c>
-      <c r="K4" t="n">
-        <v>352</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0006870366898882319</v>
+        <v>0.000800367694586912</v>
       </c>
       <c r="M4" t="n">
-        <v>2.672268265659703</v>
+        <v>2.668897073910403</v>
       </c>
       <c r="N4" t="n">
-        <v>13.16443373438018</v>
+        <v>13.13506856802077</v>
       </c>
       <c r="O4" t="n">
-        <v>3.628282477203253</v>
+        <v>3.624233514554598</v>
       </c>
       <c r="P4" t="n">
-        <v>351.6914430129014</v>
+        <v>351.6812956801966</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24671,28 +24738,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02996036587002025</v>
+        <v>-0.03095271959267568</v>
       </c>
       <c r="J5" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K5" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005571350327541635</v>
+        <v>0.005978078579883417</v>
       </c>
       <c r="M5" t="n">
-        <v>2.323374188891584</v>
+        <v>2.322134790130692</v>
       </c>
       <c r="N5" t="n">
-        <v>9.083439511038412</v>
+        <v>9.066205611694253</v>
       </c>
       <c r="O5" t="n">
-        <v>3.013874501540901</v>
+        <v>3.011014050398014</v>
       </c>
       <c r="P5" t="n">
-        <v>358.4869894337951</v>
+        <v>358.4974756787729</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -24753,28 +24820,28 @@
         <v>0.0949</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06055710253729725</v>
+        <v>-0.05879696823322745</v>
       </c>
       <c r="J6" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K6" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02516157310792577</v>
+        <v>0.02383185560687173</v>
       </c>
       <c r="M6" t="n">
-        <v>2.18085837957749</v>
+        <v>2.1836546098272</v>
       </c>
       <c r="N6" t="n">
-        <v>8.055044951719999</v>
+        <v>8.058797311630901</v>
       </c>
       <c r="O6" t="n">
-        <v>2.838141108493374</v>
+        <v>2.838802090958597</v>
       </c>
       <c r="P6" t="n">
-        <v>364.6598988335126</v>
+        <v>364.6412994177148</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -24835,28 +24902,28 @@
         <v>0.1142</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02345253599108926</v>
+        <v>-0.02398403751719819</v>
       </c>
       <c r="J7" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K7" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003251082017318385</v>
+        <v>0.003421273944298031</v>
       </c>
       <c r="M7" t="n">
-        <v>2.473301366909071</v>
+        <v>2.468762869447568</v>
       </c>
       <c r="N7" t="n">
-        <v>9.560495743213766</v>
+        <v>9.53590567542706</v>
       </c>
       <c r="O7" t="n">
-        <v>3.092005133115688</v>
+        <v>3.088026177905081</v>
       </c>
       <c r="P7" t="n">
-        <v>363.0582543281777</v>
+        <v>363.0638707279367</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -24917,28 +24984,28 @@
         <v>0.1166</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02654240782739824</v>
+        <v>0.02620063094901695</v>
       </c>
       <c r="J8" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K8" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003860680427535734</v>
+        <v>0.003786830686098641</v>
       </c>
       <c r="M8" t="n">
-        <v>2.509578645024778</v>
+        <v>2.504124306507574</v>
       </c>
       <c r="N8" t="n">
-        <v>10.3057548645311</v>
+        <v>10.27764198671832</v>
       </c>
       <c r="O8" t="n">
-        <v>3.210257756712239</v>
+        <v>3.20587616521885</v>
       </c>
       <c r="P8" t="n">
-        <v>362.0632374111959</v>
+        <v>362.0668489823449</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -24999,28 +25066,28 @@
         <v>0.1574</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06211923240956585</v>
+        <v>0.05997195553491171</v>
       </c>
       <c r="J9" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K9" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02550142837645086</v>
+        <v>0.02385453818859362</v>
       </c>
       <c r="M9" t="n">
-        <v>2.378763664823552</v>
+        <v>2.38192845203697</v>
       </c>
       <c r="N9" t="n">
-        <v>8.360106398522143</v>
+        <v>8.375939691130485</v>
       </c>
       <c r="O9" t="n">
-        <v>2.891384858250825</v>
+        <v>2.894121575043192</v>
       </c>
       <c r="P9" t="n">
-        <v>359.8307421434018</v>
+        <v>359.8534325115928</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -25081,28 +25148,28 @@
         <v>0.1396</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06061385945740513</v>
+        <v>0.0584340222908137</v>
       </c>
       <c r="J10" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K10" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01981965951977271</v>
+        <v>0.01849415810326771</v>
       </c>
       <c r="M10" t="n">
-        <v>2.244009538932414</v>
+        <v>2.249181031079898</v>
       </c>
       <c r="N10" t="n">
-        <v>10.30140867249356</v>
+        <v>10.31296351557665</v>
       </c>
       <c r="O10" t="n">
-        <v>3.209580762731102</v>
+        <v>3.211380313132757</v>
       </c>
       <c r="P10" t="n">
-        <v>358.0383640258416</v>
+        <v>358.0613984600545</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -25163,28 +25230,28 @@
         <v>0.1321</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.03166422877935191</v>
+        <v>-0.03327216993974876</v>
       </c>
       <c r="J11" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K11" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004048742305712172</v>
+        <v>0.004490993444300817</v>
       </c>
       <c r="M11" t="n">
-        <v>2.889960678966538</v>
+        <v>2.891539089490421</v>
       </c>
       <c r="N11" t="n">
-        <v>13.98294731642031</v>
+        <v>13.96556846493334</v>
       </c>
       <c r="O11" t="n">
-        <v>3.739377931744839</v>
+        <v>3.737053446892798</v>
       </c>
       <c r="P11" t="n">
-        <v>358.6310873180374</v>
+        <v>358.648078502262</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -25245,28 +25312,28 @@
         <v>0.08840000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.007413789564593538</v>
+        <v>0.005272654749220783</v>
       </c>
       <c r="J12" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K12" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0002129606596887879</v>
+        <v>0.0001081523940106299</v>
       </c>
       <c r="M12" t="n">
-        <v>2.961503237692677</v>
+        <v>2.962395242219781</v>
       </c>
       <c r="N12" t="n">
-        <v>14.62957035056226</v>
+        <v>14.62746793401694</v>
       </c>
       <c r="O12" t="n">
-        <v>3.82486213484385</v>
+        <v>3.824587289370834</v>
       </c>
       <c r="P12" t="n">
-        <v>362.2545843603071</v>
+        <v>362.2772098250904</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -25327,28 +25394,28 @@
         <v>0.09229999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.04248549700557974</v>
+        <v>-0.04364011694011349</v>
       </c>
       <c r="J13" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K13" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01489044849136101</v>
+        <v>0.01577445463736327</v>
       </c>
       <c r="M13" t="n">
-        <v>2.031050914935188</v>
+        <v>2.03062352841371</v>
       </c>
       <c r="N13" t="n">
-        <v>6.770193799902702</v>
+        <v>6.76247519976085</v>
       </c>
       <c r="O13" t="n">
-        <v>2.601959607661637</v>
+        <v>2.600475956389686</v>
       </c>
       <c r="P13" t="n">
-        <v>362.2062563758986</v>
+        <v>362.2184572949997</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -25409,28 +25476,28 @@
         <v>0.1044</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0174229651936018</v>
+        <v>-0.01923580777803163</v>
       </c>
       <c r="J14" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K14" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001525645355505256</v>
+        <v>0.001866703156121141</v>
       </c>
       <c r="M14" t="n">
-        <v>2.432391392683699</v>
+        <v>2.436310779909885</v>
       </c>
       <c r="N14" t="n">
-        <v>11.26342326632885</v>
+        <v>11.25972369987225</v>
       </c>
       <c r="O14" t="n">
-        <v>3.356102392110356</v>
+        <v>3.355551176762507</v>
       </c>
       <c r="P14" t="n">
-        <v>362.7758255563896</v>
+        <v>362.79498194288</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -25491,28 +25558,28 @@
         <v>0.1029</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.03467836844413097</v>
+        <v>-0.03501354791931012</v>
       </c>
       <c r="J15" t="n">
+        <v>354</v>
+      </c>
+      <c r="K15" t="n">
         <v>353</v>
       </c>
-      <c r="K15" t="n">
-        <v>352</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.006575067318400518</v>
+        <v>0.006745533106975454</v>
       </c>
       <c r="M15" t="n">
-        <v>2.374515281951684</v>
+        <v>2.369458894812655</v>
       </c>
       <c r="N15" t="n">
-        <v>10.32653875331306</v>
+        <v>10.29824960844445</v>
       </c>
       <c r="O15" t="n">
-        <v>3.213493232187218</v>
+        <v>3.209088594670525</v>
       </c>
       <c r="P15" t="n">
-        <v>365.7355541897739</v>
+        <v>365.7390935660312</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -25573,28 +25640,28 @@
         <v>0.1246</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00468257047695732</v>
+        <v>0.005709879979629205</v>
       </c>
       <c r="J16" t="n">
+        <v>354</v>
+      </c>
+      <c r="K16" t="n">
         <v>353</v>
       </c>
-      <c r="K16" t="n">
-        <v>352</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.0001656715547418974</v>
+        <v>0.0002476564312732243</v>
       </c>
       <c r="M16" t="n">
-        <v>2.177732506067374</v>
+        <v>2.176317141392758</v>
       </c>
       <c r="N16" t="n">
-        <v>7.520580346729909</v>
+        <v>7.508336097853873</v>
       </c>
       <c r="O16" t="n">
-        <v>2.742367653457484</v>
+        <v>2.740134321133523</v>
       </c>
       <c r="P16" t="n">
-        <v>362.0175640363022</v>
+        <v>362.0067160126853</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -25636,7 +25703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q354"/>
+  <dimension ref="A1:Q355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56425,6 +56492,93 @@
         </is>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-35.221190590606696,174.059200745573</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>-35.22180413596531,174.05869138284834</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-35.22251100164061,174.0583806861349</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-35.22325512029829,174.05826143894532</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-35.223991681732514,174.05832820725746</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-35.22472568454266,174.05829944941382</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-35.22545911729286,174.0583288320056</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-35.22619418820621,174.05830481559408</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-35.22692842347464,174.05831411427778</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>-35.227662212500775,174.05833406603531</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>-35.22839731064304,174.05840669544517</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>-35.22912294541814,174.05857882612167</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>-35.22982563349161,174.05884714154527</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>-35.23048136702635,174.0592448088889</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>-35.231090327111204,174.05974415706808</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
